--- a/artfynd/A 19401-2025 artfynd.xlsx
+++ b/artfynd/A 19401-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899997</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899999</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128899998</v>
       </c>
       <c r="B4" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128900000</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128900003</v>
       </c>
       <c r="B6" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128900001</v>
       </c>
       <c r="B7" t="n">
-        <v>91958</v>
+        <v>91962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128900002</v>
       </c>
       <c r="B8" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19401-2025 artfynd.xlsx
+++ b/artfynd/A 19401-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899997</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899999</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128899998</v>
       </c>
       <c r="B4" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128900000</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128900003</v>
       </c>
       <c r="B6" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128900001</v>
       </c>
       <c r="B7" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128900002</v>
       </c>
       <c r="B8" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19401-2025 artfynd.xlsx
+++ b/artfynd/A 19401-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899997</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899999</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128900000</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128900003</v>
       </c>
       <c r="B6" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128900001</v>
       </c>
       <c r="B7" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128900002</v>
       </c>
       <c r="B8" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19401-2025 artfynd.xlsx
+++ b/artfynd/A 19401-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899997</v>
       </c>
       <c r="B2" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899999</v>
       </c>
       <c r="B3" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128899998</v>
       </c>
       <c r="B4" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128900000</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128900003</v>
       </c>
       <c r="B6" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128900001</v>
       </c>
       <c r="B7" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128900002</v>
       </c>
       <c r="B8" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19401-2025 artfynd.xlsx
+++ b/artfynd/A 19401-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899997</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899999</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128899998</v>
       </c>
       <c r="B4" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128900000</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128900003</v>
       </c>
       <c r="B6" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128900001</v>
       </c>
       <c r="B7" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128900002</v>
       </c>
       <c r="B8" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19401-2025 artfynd.xlsx
+++ b/artfynd/A 19401-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899997</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899999</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128899998</v>
       </c>
       <c r="B4" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128900000</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128900003</v>
       </c>
       <c r="B6" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128900001</v>
       </c>
       <c r="B7" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128900002</v>
       </c>
       <c r="B8" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19401-2025 artfynd.xlsx
+++ b/artfynd/A 19401-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899997</v>
       </c>
       <c r="B2" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899999</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128899998</v>
       </c>
       <c r="B4" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128900000</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128900003</v>
       </c>
       <c r="B6" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128900001</v>
       </c>
       <c r="B7" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128900002</v>
       </c>
       <c r="B8" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19401-2025 artfynd.xlsx
+++ b/artfynd/A 19401-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899997</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899999</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128900000</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128900003</v>
       </c>
       <c r="B6" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128900001</v>
       </c>
       <c r="B7" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,7 +1260,7 @@
         <v>128900002</v>
       </c>
       <c r="B8" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19401-2025 artfynd.xlsx
+++ b/artfynd/A 19401-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128899997</v>
+        <v>128899999</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587577</v>
+        <v>587575</v>
       </c>
       <c r="R2" t="n">
-        <v>6987948</v>
+        <v>6987952</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899999</v>
+        <v>128899997</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587575</v>
+        <v>587577</v>
       </c>
       <c r="R3" t="n">
-        <v>6987952</v>
+        <v>6987948</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>128900000</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128900003</v>
       </c>
       <c r="B6" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128900001</v>
       </c>
       <c r="B7" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128900002</v>
       </c>
       <c r="B8" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19401-2025 artfynd.xlsx
+++ b/artfynd/A 19401-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128899999</v>
+        <v>128899997</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587575</v>
+        <v>587577</v>
       </c>
       <c r="R2" t="n">
-        <v>6987952</v>
+        <v>6987948</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899997</v>
+        <v>128899999</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587577</v>
+        <v>587575</v>
       </c>
       <c r="R3" t="n">
-        <v>6987948</v>
+        <v>6987952</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>128900000</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 19401-2025 artfynd.xlsx
+++ b/artfynd/A 19401-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899997</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899999</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128899998</v>
       </c>
       <c r="B4" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128900000</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128900003</v>
       </c>
       <c r="B6" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128900001</v>
       </c>
       <c r="B7" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128900002</v>
       </c>
       <c r="B8" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19401-2025 artfynd.xlsx
+++ b/artfynd/A 19401-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899997</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899999</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128899998</v>
       </c>
       <c r="B4" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128900000</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128900003</v>
       </c>
       <c r="B6" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128900001</v>
       </c>
       <c r="B7" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128900002</v>
       </c>
       <c r="B8" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19401-2025 artfynd.xlsx
+++ b/artfynd/A 19401-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128899997</v>
+        <v>128900002</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587577</v>
+        <v>587565</v>
       </c>
       <c r="R2" t="n">
-        <v>6987948</v>
+        <v>6987943</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899999</v>
+        <v>128900003</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587575</v>
+        <v>587577</v>
       </c>
       <c r="R3" t="n">
-        <v>6987952</v>
+        <v>6987942</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899998</v>
+        <v>128900001</v>
       </c>
       <c r="B4" t="n">
-        <v>83012</v>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587480</v>
+        <v>587565</v>
       </c>
       <c r="R4" t="n">
-        <v>6987920</v>
+        <v>6987943</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128900000</v>
+        <v>128899998</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587543</v>
+        <v>587480</v>
       </c>
       <c r="R5" t="n">
-        <v>6987913</v>
+        <v>6987920</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128900003</v>
+        <v>128899997</v>
       </c>
       <c r="B6" t="n">
-        <v>91843</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
         <v>587577</v>
       </c>
       <c r="R6" t="n">
-        <v>6987942</v>
+        <v>6987948</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128900001</v>
+        <v>128899999</v>
       </c>
       <c r="B7" t="n">
-        <v>91998</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587565</v>
+        <v>587575</v>
       </c>
       <c r="R7" t="n">
-        <v>6987943</v>
+        <v>6987952</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128900002</v>
+        <v>128900000</v>
       </c>
       <c r="B8" t="n">
-        <v>91843</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587565</v>
+        <v>587543</v>
       </c>
       <c r="R8" t="n">
-        <v>6987943</v>
+        <v>6987913</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 19401-2025 artfynd.xlsx
+++ b/artfynd/A 19401-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900002</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900003</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900001</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899998</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899997</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899999</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,8 +1386,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900000</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>